--- a/doc/manual/v100/WinActor for WMC提供ライブラリ一覧表_V1_0_0.xlsx
+++ b/doc/manual/v100/WinActor for WMC提供ライブラリ一覧表_V1_0_0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30140\Desktop\WMCアダプタマニュアル作成関連\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30140\Desktop\新しいフォルダー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594612DC-DEE9-4B18-8B85-5C6F27E1D797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC06CFF-70E4-488D-A6A7-C915FD90EAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="提供ライブラリ一覧" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="117">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -669,6 +669,14 @@
   </si>
   <si>
     <t>スケジュール削除を行います。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WMC連携(承認待ちスケジュール情報エクスポート)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>承認待ちスケジュール情報のエクスポートを行います。CSVファイル形式で出力されます。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -905,11 +913,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1240,45 +1248,45 @@
       <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12" t="s">
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
     </row>
     <row r="6" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13" t="s">
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -1319,14 +1327,14 @@
       <c r="A11" s="7">
         <v>1</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12" t="s">
         <v>60</v>
       </c>
       <c r="H11" s="16"/>
@@ -1348,16 +1356,16 @@
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
@@ -1392,16 +1400,16 @@
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
@@ -1521,23 +1529,23 @@
       <c r="A25" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12" t="s">
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
     </row>
     <row r="26" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
@@ -1550,16 +1558,16 @@
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
@@ -1572,16 +1580,16 @@
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
@@ -1594,16 +1602,16 @@
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
@@ -1665,23 +1673,23 @@
       <c r="A33" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12" t="s">
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
     </row>
     <row r="34" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
@@ -1791,23 +1799,23 @@
       <c r="A42" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12" t="s">
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
     </row>
     <row r="43" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
@@ -1879,13 +1887,13 @@
       <c r="A46" s="7">
         <v>4</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
       <c r="G46" s="9" t="s">
         <v>97</v>
       </c>
@@ -2103,23 +2111,23 @@
       <c r="A58" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12" t="s">
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="12"/>
-      <c r="L58" s="12"/>
-      <c r="M58" s="12"/>
-      <c r="N58" s="12"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
     </row>
     <row r="59" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
@@ -2247,23 +2255,23 @@
       <c r="A66" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12" t="s">
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H66" s="12"/>
-      <c r="I66" s="12"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="12"/>
-      <c r="L66" s="12"/>
-      <c r="M66" s="12"/>
-      <c r="N66" s="12"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
     </row>
     <row r="67" spans="1:14" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
@@ -2276,16 +2284,16 @@
       <c r="D67" s="10"/>
       <c r="E67" s="10"/>
       <c r="F67" s="11"/>
-      <c r="G67" s="13" t="s">
+      <c r="G67" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13"/>
-      <c r="K67" s="13"/>
-      <c r="L67" s="13"/>
-      <c r="M67" s="13"/>
-      <c r="N67" s="13"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
+      <c r="N67" s="12"/>
     </row>
     <row r="68" spans="1:14" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
@@ -2334,30 +2342,51 @@
     <row r="70" spans="1:14" ht="78" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="71" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="72" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
+    <row r="73" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+    <row r="74" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+    </row>
+    <row r="75" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="13"/>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13"/>
     </row>
     <row r="76" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B76" s="12" t="s">
+      <c r="A76" s="7">
         <v>1</v>
       </c>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
+      <c r="B76" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="11"/>
       <c r="G76" s="12" t="s">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
@@ -2369,39 +2398,39 @@
     </row>
     <row r="77" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
       <c r="E77" s="10"/>
       <c r="F77" s="11"/>
-      <c r="G77" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
-      <c r="J77" s="13"/>
-      <c r="K77" s="13"/>
-      <c r="L77" s="13"/>
-      <c r="M77" s="13"/>
-      <c r="N77" s="13"/>
+      <c r="G77" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H77" s="10"/>
+      <c r="I77" s="10"/>
+      <c r="J77" s="10"/>
+      <c r="K77" s="10"/>
+      <c r="L77" s="10"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="11"/>
     </row>
     <row r="78" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
       <c r="E78" s="10"/>
       <c r="F78" s="11"/>
       <c r="G78" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H78" s="10"/>
       <c r="I78" s="10"/>
@@ -2411,73 +2440,73 @@
       <c r="M78" s="10"/>
       <c r="N78" s="11"/>
     </row>
-    <row r="79" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="7">
-        <v>3</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H79" s="10"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
-      <c r="K79" s="10"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="10"/>
-      <c r="N79" s="11"/>
-    </row>
-    <row r="80" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
+    <row r="79" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
+    <row r="80" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+    </row>
+    <row r="81" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81" s="13"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13"/>
+      <c r="K81" s="13"/>
+      <c r="L81" s="13"/>
+      <c r="M81" s="13"/>
+      <c r="N81" s="13"/>
     </row>
     <row r="82" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B82" s="12" t="s">
+      <c r="A82" s="7">
         <v>1</v>
       </c>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="H82" s="12"/>
-      <c r="I82" s="12"/>
-      <c r="J82" s="12"/>
-      <c r="K82" s="12"/>
-      <c r="L82" s="12"/>
-      <c r="M82" s="12"/>
-      <c r="N82" s="12"/>
+      <c r="B82" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H82" s="10"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="10"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="11"/>
     </row>
     <row r="83" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="10"/>
       <c r="F83" s="11"/>
       <c r="G83" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H83" s="10"/>
       <c r="I83" s="10"/>
@@ -2489,17 +2518,17 @@
     </row>
     <row r="84" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
       <c r="E84" s="10"/>
       <c r="F84" s="11"/>
       <c r="G84" s="9" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H84" s="10"/>
       <c r="I84" s="10"/>
@@ -2511,17 +2540,17 @@
     </row>
     <row r="85" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
       <c r="E85" s="10"/>
       <c r="F85" s="11"/>
       <c r="G85" s="9" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="H85" s="10"/>
       <c r="I85" s="10"/>
@@ -2533,17 +2562,17 @@
     </row>
     <row r="86" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="E86" s="10"/>
       <c r="F86" s="11"/>
       <c r="G86" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H86" s="10"/>
       <c r="I86" s="10"/>
@@ -2555,17 +2584,17 @@
     </row>
     <row r="87" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
       <c r="E87" s="10"/>
       <c r="F87" s="11"/>
       <c r="G87" s="9" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="H87" s="10"/>
       <c r="I87" s="10"/>
@@ -2592,23 +2621,23 @@
       <c r="A93" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="12"/>
-      <c r="D93" s="12"/>
-      <c r="E93" s="12"/>
-      <c r="F93" s="12"/>
-      <c r="G93" s="12" t="s">
+      <c r="C93" s="13"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H93" s="12"/>
-      <c r="I93" s="12"/>
-      <c r="J93" s="12"/>
-      <c r="K93" s="12"/>
-      <c r="L93" s="12"/>
-      <c r="M93" s="12"/>
-      <c r="N93" s="12"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="13"/>
+      <c r="J93" s="13"/>
+      <c r="K93" s="13"/>
+      <c r="L93" s="13"/>
+      <c r="M93" s="13"/>
+      <c r="N93" s="13"/>
     </row>
     <row r="94" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
@@ -2721,53 +2750,61 @@
       <c r="N98" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="124">
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="G13:N13"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="G28:N28"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="G97:N97"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="G98:N98"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="G50:N50"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="G94:N94"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="G95:N95"/>
-    <mergeCell ref="B96:F96"/>
-    <mergeCell ref="G96:N96"/>
-    <mergeCell ref="B93:F93"/>
-    <mergeCell ref="G93:N93"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="G87:N87"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="G59:N59"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="G85:N85"/>
+  <mergeCells count="126">
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="G86:N86"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G20:N20"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="G37:N37"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="G66:N66"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="G27:N27"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="G67:N67"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="G68:N68"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="G58:N58"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="G61:N61"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="G62:N62"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="G84:N84"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="G82:N82"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="G81:N81"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="G69:N69"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="G42:N42"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G34:N34"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="G54:N54"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:N48"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:N47"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:N45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:N46"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="G35:N35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:N36"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="G51:N51"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="G52:N52"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="G78:N78"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="G75:N75"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="G76:N76"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="G77:N77"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="G55:N55"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="G60:N60"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="G63:N63"/>
+    <mergeCell ref="G5:N5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="G6:N6"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="G11:N11"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="G14:N14"/>
     <mergeCell ref="B15:F15"/>
@@ -2792,60 +2829,54 @@
     <mergeCell ref="G26:N26"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="G29:N29"/>
-    <mergeCell ref="G5:N5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="G6:N6"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="G12:N12"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="G11:N11"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="G85:N85"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="G37:N37"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="G66:N66"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G27:N27"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="G67:N67"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="G68:N68"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="G58:N58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="G61:N61"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="G62:N62"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="G83:N83"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="G49:N49"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="G51:N51"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="G52:N52"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="G79:N79"/>
-    <mergeCell ref="B76:F76"/>
-    <mergeCell ref="G76:N76"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="G77:N77"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="G78:N78"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="G55:N55"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="G60:N60"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="G63:N63"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="G83:N83"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="G82:N82"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="G69:N69"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="G42:N42"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G34:N34"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="G54:N54"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="G48:N48"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="G47:N47"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="G45:N45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="G46:N46"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="G35:N35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G36:N36"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="G13:N13"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="G28:N28"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="G97:N97"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="G98:N98"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="G50:N50"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="G94:N94"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="G95:N95"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="G96:N96"/>
+    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="G93:N93"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="G87:N87"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="G59:N59"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="G84:N84"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/doc/manual/v100/WinActor for WMC提供ライブラリ一覧表_V1_0_0.xlsx
+++ b/doc/manual/v100/WinActor for WMC提供ライブラリ一覧表_V1_0_0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30140\Desktop\新しいフォルダー\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30140\Desktop\manual\v100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC06CFF-70E4-488D-A6A7-C915FD90EAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B85B09-D03C-40A1-9EF5-AECE165918C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="提供ライブラリ一覧" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="119">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -677,6 +677,14 @@
   </si>
   <si>
     <t>承認待ちスケジュール情報のエクスポートを行います。CSVファイル形式で出力されます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WMC連携(FL利用状況エクスポート)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FL(フローティングライセンス)利用状況のエクスポートを行います。CSVファイル形式で出力されます。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -876,7 +884,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -913,11 +921,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -927,6 +935,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1213,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N98"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.08984375" style="1" customWidth="1"/>
@@ -1248,47 +1268,47 @@
       <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13" t="s">
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
     </row>
     <row r="6" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12" t="s">
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-    </row>
-    <row r="7" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+    </row>
+    <row r="7" spans="1:14" ht="7.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>5</v>
@@ -1327,14 +1347,14 @@
       <c r="A11" s="7">
         <v>1</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12" t="s">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13" t="s">
         <v>60</v>
       </c>
       <c r="H11" s="16"/>
@@ -1356,16 +1376,16 @@
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
     </row>
     <row r="13" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
@@ -1400,16 +1420,16 @@
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
     </row>
     <row r="15" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
@@ -1433,255 +1453,257 @@
       <c r="M15" s="10"/>
       <c r="N15" s="11"/>
     </row>
-    <row r="16" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+    </row>
+    <row r="17" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+    </row>
+    <row r="18" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+    </row>
+    <row r="19" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+    </row>
+    <row r="20" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:14" ht="60.4" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B24" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14" t="s">
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="15"/>
+    </row>
+    <row r="25" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5">
         <v>1</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B25" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="11"/>
+    </row>
+    <row r="26" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="5">
+        <v>2</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>11</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="11"/>
-    </row>
-    <row r="20" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
-        <v>2</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="11"/>
-    </row>
-    <row r="21" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:14" ht="60.4" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-    </row>
-    <row r="25" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-    </row>
-    <row r="26" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7">
-        <v>1</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>14</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-    </row>
-    <row r="27" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="7">
-        <v>2</v>
+      <c r="G26" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="11"/>
+    </row>
+    <row r="27" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5">
+        <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="11"/>
+    </row>
+    <row r="28" spans="1:14" ht="7.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="17"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+    </row>
+    <row r="29" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+    </row>
+    <row r="32" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7">
+        <v>1</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+    </row>
+    <row r="33" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="7">
+        <v>2</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="13" t="s">
         <v>83</v>
-      </c>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-    </row>
-    <row r="28" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7">
-        <v>3</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-    </row>
-    <row r="29" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7">
-        <v>4</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="11"/>
-    </row>
-    <row r="30" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7">
-        <v>5</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="11"/>
-    </row>
-    <row r="31" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-    </row>
-    <row r="33" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13" t="s">
-        <v>2</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
@@ -1693,39 +1715,39 @@
     </row>
     <row r="34" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="11"/>
+      <c r="G34" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
     </row>
     <row r="35" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="F35" s="11"/>
       <c r="G35" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
@@ -1737,17 +1759,17 @@
     </row>
     <row r="36" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="F36" s="11"/>
       <c r="G36" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
@@ -1758,100 +1780,88 @@
       <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="7">
-        <v>4</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="11"/>
-    </row>
-    <row r="38" spans="1:14" ht="61.65" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:14" ht="61.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N39"/>
-    </row>
-    <row r="40" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-    </row>
-    <row r="41" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-    </row>
-    <row r="42" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
+      <c r="A37" s="17"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+    </row>
+    <row r="38" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="17"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+    </row>
+    <row r="39" spans="1:14" ht="61.65" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:14" ht="61.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N40"/>
+    </row>
+    <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+    </row>
+    <row r="43" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B43" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13" t="s">
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
-      <c r="L42" s="13"/>
-      <c r="M42" s="13"/>
-      <c r="N42" s="13"/>
-    </row>
-    <row r="43" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="7">
-        <v>1</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="11"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
     </row>
     <row r="44" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
       <c r="F44" s="11"/>
       <c r="G44" s="9" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
@@ -1863,17 +1873,17 @@
     </row>
     <row r="45" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
       <c r="F45" s="11"/>
       <c r="G45" s="9" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
@@ -1885,17 +1895,17 @@
     </row>
     <row r="46" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
-        <v>4</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="11"/>
       <c r="G46" s="9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
@@ -1907,17 +1917,17 @@
     </row>
     <row r="47" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
       <c r="F47" s="11"/>
       <c r="G47" s="9" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
@@ -1927,107 +1937,58 @@
       <c r="M47" s="10"/>
       <c r="N47" s="11"/>
     </row>
-    <row r="48" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="7">
-        <v>6</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="11"/>
-    </row>
-    <row r="49" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="7">
-        <v>7</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="11"/>
-    </row>
-    <row r="50" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="7">
-        <v>8</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="11"/>
-    </row>
-    <row r="51" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="7">
-        <v>9</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="11"/>
+    <row r="48" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+    </row>
+    <row r="49" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+    </row>
+    <row r="50" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+      <c r="M51" s="12"/>
+      <c r="N51" s="12"/>
     </row>
     <row r="52" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
       <c r="F52" s="11"/>
       <c r="G52" s="9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H52" s="10"/>
       <c r="I52" s="10"/>
@@ -2039,17 +2000,17 @@
     </row>
     <row r="53" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
       <c r="F53" s="11"/>
       <c r="G53" s="9" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="H53" s="10"/>
       <c r="I53" s="10"/>
@@ -2061,17 +2022,17 @@
     </row>
     <row r="54" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
       <c r="F54" s="11"/>
       <c r="G54" s="9" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H54" s="10"/>
       <c r="I54" s="10"/>
@@ -2083,17 +2044,17 @@
     </row>
     <row r="55" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
-        <v>13</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="11"/>
+        <v>4</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
       <c r="G55" s="9" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H55" s="10"/>
       <c r="I55" s="10"/>
@@ -2103,89 +2064,89 @@
       <c r="M55" s="10"/>
       <c r="N55" s="11"/>
     </row>
-    <row r="56" spans="1:14" ht="61.65" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="1:14" ht="61.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N57"/>
-    </row>
-    <row r="58" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
+    <row r="56" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="7">
+        <v>5</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="11"/>
+    </row>
+    <row r="57" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="7">
+        <v>6</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="11"/>
+    </row>
+    <row r="58" spans="1:14" ht="61.65" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="1:14" ht="61.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N59"/>
+    </row>
+    <row r="60" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B60" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13" t="s">
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
-      <c r="L58" s="13"/>
-      <c r="M58" s="13"/>
-      <c r="N58" s="13"/>
-    </row>
-    <row r="59" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="7">
-        <v>14</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
-      <c r="N59" s="11"/>
-    </row>
-    <row r="60" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="7">
-        <v>15</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
-      <c r="N60" s="11"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="12"/>
+      <c r="M60" s="12"/>
+      <c r="N60" s="12"/>
     </row>
     <row r="61" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="10"/>
       <c r="F61" s="11"/>
       <c r="G61" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H61" s="10"/>
       <c r="I61" s="10"/>
@@ -2197,17 +2158,17 @@
     </row>
     <row r="62" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
       <c r="E62" s="10"/>
       <c r="F62" s="11"/>
       <c r="G62" s="9" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="H62" s="10"/>
       <c r="I62" s="10"/>
@@ -2219,17 +2180,17 @@
     </row>
     <row r="63" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
       <c r="E63" s="10"/>
       <c r="F63" s="11"/>
       <c r="G63" s="9" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="H63" s="10"/>
       <c r="I63" s="10"/>
@@ -2239,75 +2200,107 @@
       <c r="M63" s="10"/>
       <c r="N63" s="11"/>
     </row>
-    <row r="64" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-    </row>
-    <row r="65" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-    </row>
-    <row r="66" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="13"/>
-      <c r="L66" s="13"/>
-      <c r="M66" s="13"/>
-      <c r="N66" s="13"/>
-    </row>
-    <row r="67" spans="1:14" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="7">
+        <v>10</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H64" s="10"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="11"/>
+    </row>
+    <row r="65" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="7">
+        <v>11</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H65" s="10"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="11"/>
+    </row>
+    <row r="66" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="7">
+        <v>12</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H66" s="10"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="11"/>
+    </row>
+    <row r="67" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
       <c r="E67" s="10"/>
       <c r="F67" s="11"/>
-      <c r="G67" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="H67" s="12"/>
-      <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="12"/>
-      <c r="N67" s="12"/>
-    </row>
-    <row r="68" spans="1:14" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G67" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H67" s="10"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="11"/>
+    </row>
+    <row r="68" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
       <c r="E68" s="10"/>
       <c r="F68" s="11"/>
       <c r="G68" s="9" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="H68" s="10"/>
       <c r="I68" s="10"/>
@@ -2317,19 +2310,19 @@
       <c r="M68" s="10"/>
       <c r="N68" s="11"/>
     </row>
-    <row r="69" spans="1:14" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
       <c r="E69" s="10"/>
       <c r="F69" s="11"/>
       <c r="G69" s="9" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="H69" s="10"/>
       <c r="I69" s="10"/>
@@ -2339,130 +2332,169 @@
       <c r="M69" s="10"/>
       <c r="N69" s="11"/>
     </row>
-    <row r="70" spans="1:14" ht="78" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
+    <row r="70" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="7">
+        <v>16</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H70" s="10"/>
+      <c r="I70" s="10"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="10"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="11"/>
+    </row>
+    <row r="71" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="7">
+        <v>17</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="11"/>
+    </row>
+    <row r="72" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="7">
+        <v>18</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H72" s="10"/>
+      <c r="I72" s="10"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="10"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="11"/>
+    </row>
+    <row r="73" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="17"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18"/>
+      <c r="N73" s="18"/>
+    </row>
+    <row r="74" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="17"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="18"/>
+      <c r="L74" s="18"/>
+      <c r="M74" s="18"/>
+      <c r="N74" s="18"/>
     </row>
     <row r="75" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="17"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="18"/>
+      <c r="L75" s="18"/>
+      <c r="M75" s="18"/>
+      <c r="N75" s="18"/>
+    </row>
+    <row r="76" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+    </row>
+    <row r="79" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+    </row>
+    <row r="80" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B80" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13" t="s">
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13"/>
-      <c r="K75" s="13"/>
-      <c r="L75" s="13"/>
-      <c r="M75" s="13"/>
-      <c r="N75" s="13"/>
-    </row>
-    <row r="76" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="7">
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="12"/>
+      <c r="K80" s="12"/>
+      <c r="L80" s="12"/>
+      <c r="M80" s="12"/>
+      <c r="N80" s="12"/>
+    </row>
+    <row r="81" spans="1:14" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="7">
         <v>1</v>
       </c>
-      <c r="B76" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H76" s="12"/>
-      <c r="I76" s="12"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="12"/>
-      <c r="L76" s="12"/>
-      <c r="M76" s="12"/>
-      <c r="N76" s="12"/>
-    </row>
-    <row r="77" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="7">
-        <v>2</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H77" s="10"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="10"/>
-      <c r="L77" s="10"/>
-      <c r="M77" s="10"/>
-      <c r="N77" s="11"/>
-    </row>
-    <row r="78" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="7">
-        <v>3</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="10"/>
-      <c r="N78" s="11"/>
-    </row>
-    <row r="79" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-    </row>
-    <row r="81" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B81" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C81" s="13"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
+      <c r="B81" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="11"/>
       <c r="G81" s="13" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H81" s="13"/>
       <c r="I81" s="13"/>
@@ -2472,19 +2504,19 @@
       <c r="M81" s="13"/>
       <c r="N81" s="13"/>
     </row>
-    <row r="82" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
       <c r="E82" s="10"/>
       <c r="F82" s="11"/>
       <c r="G82" s="9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H82" s="10"/>
       <c r="I82" s="10"/>
@@ -2494,19 +2526,19 @@
       <c r="M82" s="10"/>
       <c r="N82" s="11"/>
     </row>
-    <row r="83" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="10"/>
       <c r="F83" s="11"/>
       <c r="G83" s="9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H83" s="10"/>
       <c r="I83" s="10"/>
@@ -2516,285 +2548,569 @@
       <c r="M83" s="10"/>
       <c r="N83" s="11"/>
     </row>
-    <row r="84" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="7">
+    <row r="84" spans="1:14" ht="7.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="17"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="18"/>
+      <c r="J84" s="18"/>
+      <c r="K84" s="18"/>
+      <c r="L84" s="18"/>
+      <c r="M84" s="18"/>
+      <c r="N84" s="18"/>
+    </row>
+    <row r="85" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+    </row>
+    <row r="87" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H87" s="12"/>
+      <c r="I87" s="12"/>
+      <c r="J87" s="12"/>
+      <c r="K87" s="12"/>
+      <c r="L87" s="12"/>
+      <c r="M87" s="12"/>
+      <c r="N87" s="12"/>
+    </row>
+    <row r="88" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="7">
+        <v>1</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C88" s="10"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13"/>
+      <c r="J88" s="13"/>
+      <c r="K88" s="13"/>
+      <c r="L88" s="13"/>
+      <c r="M88" s="13"/>
+      <c r="N88" s="13"/>
+    </row>
+    <row r="89" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="7">
+        <v>2</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C89" s="10"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H89" s="10"/>
+      <c r="I89" s="10"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="10"/>
+      <c r="L89" s="10"/>
+      <c r="M89" s="10"/>
+      <c r="N89" s="11"/>
+    </row>
+    <row r="90" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="7">
         <v>3</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B90" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C90" s="10"/>
+      <c r="D90" s="10"/>
+      <c r="E90" s="10"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H90" s="10"/>
+      <c r="I90" s="10"/>
+      <c r="J90" s="10"/>
+      <c r="K90" s="10"/>
+      <c r="L90" s="10"/>
+      <c r="M90" s="10"/>
+      <c r="N90" s="11"/>
+    </row>
+    <row r="91" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="17"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="18"/>
+      <c r="E91" s="18"/>
+      <c r="F91" s="18"/>
+      <c r="G91" s="18"/>
+      <c r="H91" s="18"/>
+      <c r="I91" s="18"/>
+      <c r="J91" s="18"/>
+      <c r="K91" s="18"/>
+      <c r="L91" s="18"/>
+      <c r="M91" s="18"/>
+      <c r="N91" s="18"/>
+    </row>
+    <row r="92" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="17"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="18"/>
+      <c r="H92" s="18"/>
+      <c r="I92" s="18"/>
+      <c r="J92" s="18"/>
+      <c r="K92" s="18"/>
+      <c r="L92" s="18"/>
+      <c r="M92" s="18"/>
+      <c r="N92" s="18"/>
+    </row>
+    <row r="93" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="17"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="18"/>
+      <c r="H93" s="18"/>
+      <c r="I93" s="18"/>
+      <c r="J93" s="18"/>
+      <c r="K93" s="18"/>
+      <c r="L93" s="18"/>
+      <c r="M93" s="18"/>
+      <c r="N93" s="18"/>
+    </row>
+    <row r="94" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="17"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="18"/>
+      <c r="H94" s="18"/>
+      <c r="I94" s="18"/>
+      <c r="J94" s="18"/>
+      <c r="K94" s="18"/>
+      <c r="L94" s="18"/>
+      <c r="M94" s="18"/>
+      <c r="N94" s="18"/>
+    </row>
+    <row r="95" spans="1:14" ht="58.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" spans="1:14" ht="58.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+    </row>
+    <row r="99" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" s="12"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="12"/>
+      <c r="L99" s="12"/>
+      <c r="M99" s="12"/>
+      <c r="N99" s="12"/>
+    </row>
+    <row r="100" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="7">
+        <v>1</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C100" s="10"/>
+      <c r="D100" s="10"/>
+      <c r="E100" s="10"/>
+      <c r="F100" s="11"/>
+      <c r="G100" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H100" s="10"/>
+      <c r="I100" s="10"/>
+      <c r="J100" s="10"/>
+      <c r="K100" s="10"/>
+      <c r="L100" s="10"/>
+      <c r="M100" s="10"/>
+      <c r="N100" s="11"/>
+    </row>
+    <row r="101" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="7">
+        <v>2</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C101" s="10"/>
+      <c r="D101" s="10"/>
+      <c r="E101" s="10"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H101" s="10"/>
+      <c r="I101" s="10"/>
+      <c r="J101" s="10"/>
+      <c r="K101" s="10"/>
+      <c r="L101" s="10"/>
+      <c r="M101" s="10"/>
+      <c r="N101" s="11"/>
+    </row>
+    <row r="102" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="7">
+        <v>3</v>
+      </c>
+      <c r="B102" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="9" t="s">
+      <c r="C102" s="10"/>
+      <c r="D102" s="10"/>
+      <c r="E102" s="10"/>
+      <c r="F102" s="11"/>
+      <c r="G102" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="H84" s="10"/>
-      <c r="I84" s="10"/>
-      <c r="J84" s="10"/>
-      <c r="K84" s="10"/>
-      <c r="L84" s="10"/>
-      <c r="M84" s="10"/>
-      <c r="N84" s="11"/>
-    </row>
-    <row r="85" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="7">
+      <c r="H102" s="10"/>
+      <c r="I102" s="10"/>
+      <c r="J102" s="10"/>
+      <c r="K102" s="10"/>
+      <c r="L102" s="10"/>
+      <c r="M102" s="10"/>
+      <c r="N102" s="11"/>
+    </row>
+    <row r="103" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="7">
         <v>4</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B103" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="9" t="s">
+      <c r="C103" s="10"/>
+      <c r="D103" s="10"/>
+      <c r="E103" s="10"/>
+      <c r="F103" s="11"/>
+      <c r="G103" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H85" s="10"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="10"/>
-      <c r="N85" s="11"/>
-    </row>
-    <row r="86" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="7">
+      <c r="H103" s="10"/>
+      <c r="I103" s="10"/>
+      <c r="J103" s="10"/>
+      <c r="K103" s="10"/>
+      <c r="L103" s="10"/>
+      <c r="M103" s="10"/>
+      <c r="N103" s="11"/>
+    </row>
+    <row r="104" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="7">
         <v>5</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B104" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="9" t="s">
+      <c r="C104" s="10"/>
+      <c r="D104" s="10"/>
+      <c r="E104" s="10"/>
+      <c r="F104" s="11"/>
+      <c r="G104" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H86" s="10"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="10"/>
-      <c r="N86" s="11"/>
-    </row>
-    <row r="87" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="7">
+      <c r="H104" s="10"/>
+      <c r="I104" s="10"/>
+      <c r="J104" s="10"/>
+      <c r="K104" s="10"/>
+      <c r="L104" s="10"/>
+      <c r="M104" s="10"/>
+      <c r="N104" s="11"/>
+    </row>
+    <row r="105" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="7">
         <v>6</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B105" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="9" t="s">
+      <c r="C105" s="10"/>
+      <c r="D105" s="10"/>
+      <c r="E105" s="10"/>
+      <c r="F105" s="11"/>
+      <c r="G105" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="H87" s="10"/>
-      <c r="I87" s="10"/>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10"/>
-      <c r="L87" s="10"/>
-      <c r="M87" s="10"/>
-      <c r="N87" s="11"/>
-    </row>
-    <row r="88" spans="1:14" ht="58.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" spans="1:14" ht="58.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" spans="1:14" ht="58.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="2" t="s">
+      <c r="H105" s="10"/>
+      <c r="I105" s="10"/>
+      <c r="J105" s="10"/>
+      <c r="K105" s="10"/>
+      <c r="L105" s="10"/>
+      <c r="M105" s="10"/>
+      <c r="N105" s="11"/>
+    </row>
+    <row r="106" spans="1:14" ht="7.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-    </row>
-    <row r="93" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="6" t="s">
+    <row r="108" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+    </row>
+    <row r="109" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B109" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="13"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13" t="s">
+      <c r="C109" s="12"/>
+      <c r="D109" s="12"/>
+      <c r="E109" s="12"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H93" s="13"/>
-      <c r="I93" s="13"/>
-      <c r="J93" s="13"/>
-      <c r="K93" s="13"/>
-      <c r="L93" s="13"/>
-      <c r="M93" s="13"/>
-      <c r="N93" s="13"/>
-    </row>
-    <row r="94" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="7">
+      <c r="H109" s="12"/>
+      <c r="I109" s="12"/>
+      <c r="J109" s="12"/>
+      <c r="K109" s="12"/>
+      <c r="L109" s="12"/>
+      <c r="M109" s="12"/>
+      <c r="N109" s="12"/>
+    </row>
+    <row r="110" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="7">
         <v>1</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B110" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="9" t="s">
+      <c r="C110" s="10"/>
+      <c r="D110" s="10"/>
+      <c r="E110" s="10"/>
+      <c r="F110" s="11"/>
+      <c r="G110" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
-      <c r="N94" s="11"/>
-    </row>
-    <row r="95" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="7">
+      <c r="H110" s="10"/>
+      <c r="I110" s="10"/>
+      <c r="J110" s="10"/>
+      <c r="K110" s="10"/>
+      <c r="L110" s="10"/>
+      <c r="M110" s="10"/>
+      <c r="N110" s="11"/>
+    </row>
+    <row r="111" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="7">
         <v>2</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B111" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="10"/>
-      <c r="F95" s="11"/>
-      <c r="G95" s="9" t="s">
+      <c r="C111" s="10"/>
+      <c r="D111" s="10"/>
+      <c r="E111" s="10"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="H95" s="10"/>
-      <c r="I95" s="10"/>
-      <c r="J95" s="10"/>
-      <c r="K95" s="10"/>
-      <c r="L95" s="10"/>
-      <c r="M95" s="10"/>
-      <c r="N95" s="11"/>
-    </row>
-    <row r="96" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="7">
+      <c r="H111" s="10"/>
+      <c r="I111" s="10"/>
+      <c r="J111" s="10"/>
+      <c r="K111" s="10"/>
+      <c r="L111" s="10"/>
+      <c r="M111" s="10"/>
+      <c r="N111" s="11"/>
+    </row>
+    <row r="112" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="7">
         <v>3</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B112" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="10"/>
-      <c r="E96" s="10"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="9" t="s">
+      <c r="C112" s="10"/>
+      <c r="D112" s="10"/>
+      <c r="E112" s="10"/>
+      <c r="F112" s="11"/>
+      <c r="G112" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="H96" s="10"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="10"/>
-      <c r="M96" s="10"/>
-      <c r="N96" s="11"/>
-    </row>
-    <row r="97" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="7">
+      <c r="H112" s="10"/>
+      <c r="I112" s="10"/>
+      <c r="J112" s="10"/>
+      <c r="K112" s="10"/>
+      <c r="L112" s="10"/>
+      <c r="M112" s="10"/>
+      <c r="N112" s="11"/>
+    </row>
+    <row r="113" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="7">
         <v>4</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B113" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="10"/>
-      <c r="E97" s="10"/>
-      <c r="F97" s="11"/>
-      <c r="G97" s="9" t="s">
+      <c r="C113" s="10"/>
+      <c r="D113" s="10"/>
+      <c r="E113" s="10"/>
+      <c r="F113" s="11"/>
+      <c r="G113" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H97" s="10"/>
-      <c r="I97" s="10"/>
-      <c r="J97" s="10"/>
-      <c r="K97" s="10"/>
-      <c r="L97" s="10"/>
-      <c r="M97" s="10"/>
-      <c r="N97" s="11"/>
-    </row>
-    <row r="98" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="7">
+      <c r="H113" s="10"/>
+      <c r="I113" s="10"/>
+      <c r="J113" s="10"/>
+      <c r="K113" s="10"/>
+      <c r="L113" s="10"/>
+      <c r="M113" s="10"/>
+      <c r="N113" s="11"/>
+    </row>
+    <row r="114" spans="1:14" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="7">
         <v>5</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B114" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C98" s="10"/>
-      <c r="D98" s="10"/>
-      <c r="E98" s="10"/>
-      <c r="F98" s="11"/>
-      <c r="G98" s="9" t="s">
+      <c r="C114" s="10"/>
+      <c r="D114" s="10"/>
+      <c r="E114" s="10"/>
+      <c r="F114" s="11"/>
+      <c r="G114" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H98" s="10"/>
-      <c r="I98" s="10"/>
-      <c r="J98" s="10"/>
-      <c r="K98" s="10"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="10"/>
-      <c r="N98" s="11"/>
+      <c r="H114" s="10"/>
+      <c r="I114" s="10"/>
+      <c r="J114" s="10"/>
+      <c r="K114" s="10"/>
+      <c r="L114" s="10"/>
+      <c r="M114" s="10"/>
+      <c r="N114" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="126">
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="G86:N86"/>
+  <mergeCells count="128">
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="G25:N25"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="G60:N60"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="G13:N13"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G34:N34"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="G113:N113"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="G114:N114"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="G62:N62"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="G110:N110"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="G111:N111"/>
+    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="G112:N112"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="G109:N109"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="G105:N105"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="G68:N68"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="G102:N102"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="G103:N103"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G27:N27"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:N47"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="G80:N80"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="G81:N81"/>
     <mergeCell ref="B82:F82"/>
     <mergeCell ref="G82:N82"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="G81:N81"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="G69:N69"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="G42:N42"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G34:N34"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="G54:N54"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="G48:N48"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="G47:N47"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="G45:N45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="G46:N46"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="G70:N70"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="G71:N71"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="G101:N101"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="G61:N61"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G14:N14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:N15"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G26:N26"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="G65:N65"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="G53:N53"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="G52:N52"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G31:N31"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:N36"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="G24:N24"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:N43"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="G32:N32"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="G35:N35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G36:N36"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="G51:N51"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="G52:N52"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="G78:N78"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="G75:N75"/>
-    <mergeCell ref="B76:F76"/>
-    <mergeCell ref="G76:N76"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="G77:N77"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="G55:N55"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="G60:N60"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="G63:N63"/>
     <mergeCell ref="G5:N5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
@@ -2805,78 +3121,50 @@
     <mergeCell ref="G10:N10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="G11:N11"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="G14:N14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="G15:N15"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="G19:N19"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="G53:N53"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="G44:N44"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="G43:N43"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="G25:N25"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="G30:N30"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="G18:N18"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="G33:N33"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="G26:N26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="G29:N29"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="G85:N85"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G20:N20"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="G37:N37"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="G66:N66"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="G27:N27"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="G57:N57"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="G56:N56"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="G54:N54"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="G55:N55"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:N45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:N46"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="G63:N63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="G64:N64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="G104:N104"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="G100:N100"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="G99:N99"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="G83:N83"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="G51:N51"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="G90:N90"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="G87:N87"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="G88:N88"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="G89:N89"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="G67:N67"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="G68:N68"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="G58:N58"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="G61:N61"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="G62:N62"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="G83:N83"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="G49:N49"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="G13:N13"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="G28:N28"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="G97:N97"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="G98:N98"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="G50:N50"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="G94:N94"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="G95:N95"/>
-    <mergeCell ref="B96:F96"/>
-    <mergeCell ref="G96:N96"/>
-    <mergeCell ref="B93:F93"/>
-    <mergeCell ref="G93:N93"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="G87:N87"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="G59:N59"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="G84:N84"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="G69:N69"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="G72:N72"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
